--- a/log_params.xlsx
+++ b/log_params.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="196">
   <si>
     <t>Report Date</t>
   </si>
@@ -55,6 +55,9 @@
     <t>2025-03-10</t>
   </si>
   <si>
+    <t>2025-04-09</t>
+  </si>
+  <si>
     <t>13:13:07</t>
   </si>
   <si>
@@ -251,6 +254,12 @@
   </si>
   <si>
     <t>23:35:31</t>
+  </si>
+  <si>
+    <t>23:28:52</t>
+  </si>
+  <si>
+    <t>23:28:58</t>
   </si>
   <si>
     <t>israel_24hr</t>
@@ -905,6 +914,30 @@
       dtype='object', name='Time')</t>
   </si>
   <si>
+    <t>Index(['2025-04-08 08:40:00', '2025-04-08 08:50:00', '2025-04-08 08:55:00',
+       '2025-04-08 09:10:00', '2025-04-08 09:35:00', '2025-04-08 09:45:00',
+       '2025-04-08 09:55:00', '2025-04-08 10:05:00', '2025-04-08 10:15:00',
+       '2025-04-08 10:25:00', '2025-04-08 10:35:00', '2025-04-08 10:45:00',
+       '2025-04-08 10:55:00', '2025-04-08 11:05:00', '2025-04-08 11:15:00',
+       '2025-04-08 11:25:00', '2025-04-08 11:35:00', '2025-04-08 11:45:00',
+       '2025-04-08 11:55:00', '2025-04-08 12:05:00', '2025-04-08 12:15:00',
+       '2025-04-08 12:25:00', '2025-04-08 12:35:00', '2025-04-08 12:45:00',
+       '2025-04-08 12:55:00', '2025-04-08 18:05:00', '2025-04-08 18:15:00',
+       '2025-04-08 18:25:00', '2025-04-08 18:35:00', '2025-04-08 18:45:00',
+       '2025-04-08 18:55:00', '2025-04-08 19:05:00', '2025-04-08 19:15:00',
+       '2025-04-08 19:25:00', '2025-04-08 19:35:00', '2025-04-08 19:45:00',
+       '2025-04-08 19:55:00', '2025-04-08 20:05:00', '2025-04-08 20:25:00',
+       '2025-04-08 20:40:00', '2025-04-08 20:50:00', '2025-04-08 21:10:00',
+       '2025-04-08 21:20:00', '2025-04-08 21:40:00', '2025-04-08 21:50:00',
+       '2025-04-08 22:10:00', '2025-04-08 22:20:00', '2025-04-08 22:40:00',
+       '2025-04-08 22:50:00', '2025-04-08 23:10:00', '2025-04-08 23:20:00',
+       '2025-04-08 23:40:00', '2025-04-08 23:50:00'],
+      dtype='object', name='Time')</t>
+  </si>
+  <si>
+    <t>Index(['2025-04-08 09:30:00'], dtype='object', name='Time')</t>
+  </si>
+  <si>
     <t>[429.7, 428.0, 407.73333333333335, 389.425, 355.21999999999997, 325.8833333333333, 393.2, 463.25, 510.35555555555555, 538.54, 554.8272727272728, 557.1333333333333, 548.4615384615385, 537.0714285714286, 525.8866666666667, 516.3125, 507.8411764705882, 501.65000000000003, 494.5368421052632, 486.95, 479.6952380952381, 472.24090909090904, 460.38260869565215, 441.50416666666666, 423.98400000000004, 407.7192307692308, 392.61851851851856, 378.5964285714286, 365.7655172413793, 354.33, 343.6064516129032, 333.271875, 323.5424242424242, 314.2911764705882, 305.65142857142854, 297.18055555555554, 289.46216216216214, 282.3, 275.7923076923077, 269.72249999999997, 263.51707317073175, 257.3880952380952, 252.0604651162791, 246.61136363636362, 241.5, 236.70000000000002, 231.66382978723405, 222.5212765957447, 213.67234042553193, 206.4127659574468, 199.5574468085106, 195.10851063829787, 191.68085106382978, 174.96382978723406, 154.7340425531915, 136.11063829787236]</t>
   </si>
   <si>
@@ -1065,6 +1098,12 @@
   </si>
   <si>
     <t>[397.6, 291.73333333333335]</t>
+  </si>
+  <si>
+    <t>[38.122368421052634, 38.76692307692308, 39.29825, 39.65682926829268, 39.72690476190476, 39.74906976744186, 39.882954545454545, 40.025111111111116, 39.928695652173914, 39.66340425531915, 39.41708333333333, 39.24387755102041, 39.0512, 38.91294117647059, 38.78269230769231, 38.63603773584906, 38.47555555555555, 38.30618181818182, 38.17928571428571, 38.08052631578948, 38.00534482758621, 37.95135593220339, 37.89, 37.77967213114754, 37.6283870967742, 37.611935483870965, 37.78882978723404, 37.967684210526315, 38.19135416666666, 38.37659793814433, 38.47632653061224, 38.525454545454544, 38.5322, 38.54653465346534, 38.57009803921569, 38.648640776699025, 38.785288461538464, 38.94952380952381, 39.0, 39.01401869158879, 39.042500000000004, 39.079816513761465, 39.13245454545454, 39.19198198198198, 39.25633928571428, 39.341061946902656, 39.423508771929825, 39.49895652173913, 39.59448275862069, 39.69299145299145, 39.784322033898306, 39.87058823529412, 39.955333333333336]</t>
+  </si>
+  <si>
+    <t>[38.86]</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1456,22 +1495,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H2">
         <v>130</v>
@@ -1482,22 +1521,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H3">
         <v>130</v>
@@ -1508,22 +1547,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H4">
         <v>130</v>
@@ -1534,22 +1573,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H5">
         <v>130</v>
@@ -1560,22 +1599,22 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H6">
         <v>37.5</v>
@@ -1586,22 +1625,22 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G7" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H7">
         <v>37.5</v>
@@ -1612,22 +1651,22 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G8" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H8">
         <v>130</v>
@@ -1638,22 +1677,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G9" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H9">
         <v>130</v>
@@ -1664,22 +1703,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G10" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H10">
         <v>130</v>
@@ -1690,22 +1729,22 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H11">
         <v>130</v>
@@ -1716,22 +1755,22 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H12">
         <v>37.5</v>
@@ -1742,22 +1781,22 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G13" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H13">
         <v>37.5</v>
@@ -1768,22 +1807,22 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G14" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H14">
         <v>130</v>
@@ -1794,22 +1833,22 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H15">
         <v>130</v>
@@ -1820,22 +1859,22 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H16">
         <v>130</v>
@@ -1846,22 +1885,22 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H17">
         <v>130</v>
@@ -1872,22 +1911,22 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G18" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H18">
         <v>37.5</v>
@@ -1898,22 +1937,22 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G19" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H19">
         <v>37.5</v>
@@ -1924,22 +1963,22 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G20" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="H20">
         <v>37.5</v>
@@ -1950,22 +1989,22 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G21" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H21">
         <v>37.5</v>
@@ -1976,22 +2015,22 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H22">
         <v>130</v>
@@ -2002,22 +2041,22 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H23">
         <v>130</v>
@@ -2028,22 +2067,22 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G24" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H24">
         <v>130</v>
@@ -2054,22 +2093,22 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G25" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H25">
         <v>130</v>
@@ -2080,22 +2119,22 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G26" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H26">
         <v>130</v>
@@ -2106,22 +2145,22 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G27" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H27">
         <v>130</v>
@@ -2132,22 +2171,22 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G28" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H28">
         <v>130</v>
@@ -2158,22 +2197,22 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G29" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H29">
         <v>130</v>
@@ -2184,22 +2223,22 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G30" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H30">
         <v>37.5</v>
@@ -2210,22 +2249,22 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F31" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G31" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H31">
         <v>37.5</v>
@@ -2236,22 +2275,22 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F32" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G32" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H32">
         <v>37.5</v>
@@ -2262,22 +2301,22 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E33" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G33" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H33">
         <v>37.5</v>
@@ -2288,22 +2327,22 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G34" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H34">
         <v>130</v>
@@ -2314,22 +2353,22 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E35" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G35" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H35">
         <v>130</v>
@@ -2340,22 +2379,22 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G36" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H36">
         <v>130</v>
@@ -2366,22 +2405,22 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E37" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F37" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G37" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H37">
         <v>130</v>
@@ -2392,22 +2431,22 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F38" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G38" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H38">
         <v>130</v>
@@ -2418,22 +2457,22 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D39" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E39" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G39" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H39">
         <v>130</v>
@@ -2444,22 +2483,22 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F40" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G40" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H40">
         <v>130</v>
@@ -2470,22 +2509,22 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F41" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G41" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="H41">
         <v>130</v>
@@ -2496,22 +2535,22 @@
         <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E42" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F42" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G42" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H42">
         <v>37.5</v>
@@ -2522,22 +2561,22 @@
         <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F43" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G43" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H43">
         <v>37.5</v>
@@ -2548,22 +2587,22 @@
         <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E44" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F44" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G44" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H44">
         <v>37.5</v>
@@ -2574,22 +2613,22 @@
         <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E45" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F45" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G45" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H45">
         <v>37.5</v>
@@ -2600,22 +2639,22 @@
         <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E46" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F46" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G46" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H46">
         <v>130</v>
@@ -2626,22 +2665,22 @@
         <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D47" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E47" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F47" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G47" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H47">
         <v>130</v>
@@ -2652,22 +2691,22 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D48" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E48" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F48" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G48" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H48">
         <v>130</v>
@@ -2678,22 +2717,22 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D49" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E49" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F49" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G49" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H49">
         <v>130</v>
@@ -2704,22 +2743,22 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D50" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E50" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G50" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H50">
         <v>37.5</v>
@@ -2730,22 +2769,22 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E51" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F51" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G51" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H51">
         <v>37.5</v>
@@ -2756,22 +2795,22 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F52" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G52" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H52">
         <v>130</v>
@@ -2782,22 +2821,22 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D53" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F53" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G53" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H53">
         <v>130</v>
@@ -2808,22 +2847,22 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E54" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F54" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G54" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H54">
         <v>130</v>
@@ -2834,22 +2873,22 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D55" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E55" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F55" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G55" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H55">
         <v>130</v>
@@ -2860,22 +2899,22 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D56" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E56" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F56" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G56" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H56">
         <v>37.5</v>
@@ -2886,22 +2925,22 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D57" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E57" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F57" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G57" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H57">
         <v>37.5</v>
@@ -2912,22 +2951,22 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E58" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F58" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G58" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H58">
         <v>37.5</v>
@@ -2938,22 +2977,22 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D59" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E59" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F59" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G59" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H59">
         <v>130</v>
@@ -2964,22 +3003,22 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D60" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E60" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F60" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G60" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H60">
         <v>130</v>
@@ -2990,22 +3029,22 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D61" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E61" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F61" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G61" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H61">
         <v>130</v>
@@ -3016,22 +3055,22 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D62" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E62" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F62" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G62" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H62">
         <v>130</v>
@@ -3042,22 +3081,22 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D63" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E63" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F63" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G63" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H63">
         <v>37.5</v>
@@ -3068,22 +3107,22 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D64" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E64" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F64" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G64" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H64">
         <v>37.5</v>
@@ -3094,22 +3133,22 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D65" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E65" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F65" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G65" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H65">
         <v>37.5</v>
@@ -3120,22 +3159,22 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D66" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E66" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F66" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G66" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H66">
         <v>130</v>
@@ -3146,22 +3185,22 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E67" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F67" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G67" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H67">
         <v>130</v>
@@ -3172,22 +3211,22 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E68" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F68" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G68" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H68">
         <v>130</v>
@@ -3198,22 +3237,22 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D69" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E69" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F69" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G69" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H69">
         <v>130</v>
@@ -3224,22 +3263,22 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D70" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E70" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F70" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G70" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="H70">
         <v>37.5</v>
@@ -3250,22 +3289,22 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D71" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E71" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F71" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G71" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H71">
         <v>37.5</v>
@@ -3276,22 +3315,22 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D72" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E72" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F72" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G72" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H72">
         <v>37.5</v>
@@ -3302,22 +3341,22 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E73" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F73" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G73" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H73">
         <v>130</v>
@@ -3328,22 +3367,22 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D74" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E74" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F74" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G74" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H74">
         <v>130</v>
@@ -3354,22 +3393,22 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D75" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E75" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F75" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G75" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H75">
         <v>130</v>
@@ -3380,22 +3419,22 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D76" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E76" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F76" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G76" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H76">
         <v>130</v>
@@ -3406,22 +3445,22 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E77" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F77" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G77" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H77">
         <v>130</v>
@@ -3432,22 +3471,22 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D78" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E78" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F78" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G78" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H78">
         <v>130</v>
@@ -3458,22 +3497,22 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D79" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E79" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F79" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G79" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H79">
         <v>130</v>
@@ -3484,22 +3523,22 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D80" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E80" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F80" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G80" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H80">
         <v>130</v>
@@ -3510,25 +3549,77 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D81" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" t="s">
+        <v>89</v>
+      </c>
+      <c r="F81" t="s">
+        <v>135</v>
+      </c>
+      <c r="G81" t="s">
+        <v>190</v>
+      </c>
+      <c r="H81">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>13</v>
+      </c>
+      <c r="B82" t="s">
         <v>80</v>
       </c>
-      <c r="E81" t="s">
-        <v>86</v>
-      </c>
-      <c r="F81" t="s">
-        <v>132</v>
-      </c>
-      <c r="G81" t="s">
-        <v>185</v>
-      </c>
-      <c r="H81">
-        <v>130</v>
+      <c r="C82" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" t="s">
+        <v>85</v>
+      </c>
+      <c r="E82" t="s">
+        <v>90</v>
+      </c>
+      <c r="F82" t="s">
+        <v>138</v>
+      </c>
+      <c r="G82" t="s">
+        <v>194</v>
+      </c>
+      <c r="H82">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>13</v>
+      </c>
+      <c r="B83" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" t="s">
+        <v>84</v>
+      </c>
+      <c r="E83" t="s">
+        <v>90</v>
+      </c>
+      <c r="F83" t="s">
+        <v>139</v>
+      </c>
+      <c r="G83" t="s">
+        <v>195</v>
+      </c>
+      <c r="H83">
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>
